--- a/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0196AF-066F-4925-86EE-E180A2E2DEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAVN" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>NAVN</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:J102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -668,21 +669,20 @@
     <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -707,17 +707,8 @@
       <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -742,17 +733,8 @@
       <c r="J8" s="3">
         <v>126900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,17 +759,8 @@
       <c r="J9" s="3">
         <v>41300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -812,17 +785,8 @@
       <c r="J10" s="3">
         <v>85600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,11 +797,8 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -862,17 +823,8 @@
       <c r="J12" s="3">
         <v>28900</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -897,17 +849,8 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -932,17 +875,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -967,17 +901,8 @@
       <c r="J15" s="3">
         <v>2600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -985,11 +910,8 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1014,17 +936,8 @@
       <c r="J17" s="3">
         <v>154500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1049,17 +962,8 @@
       <c r="J18" s="3">
         <v>-27700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,11 +974,8 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1099,17 +1000,8 @@
       <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1134,17 +1026,8 @@
       <c r="J21" s="3">
         <v>-23800</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1169,17 +1052,8 @@
       <c r="J22" s="3">
         <v>18900</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1204,17 +1078,8 @@
       <c r="J23" s="3">
         <v>-44100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1239,17 +1104,8 @@
       <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1274,17 +1130,8 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1309,17 +1156,8 @@
       <c r="J26" s="3">
         <v>-46300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1344,17 +1182,8 @@
       <c r="J27" s="3">
         <v>-46300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1379,17 +1208,8 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1414,17 +1234,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1449,17 +1260,8 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1484,17 +1286,8 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1519,17 +1312,8 @@
       <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1554,17 +1338,8 @@
       <c r="J33" s="3">
         <v>-46300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1589,17 +1364,8 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1624,22 +1390,13 @@
       <c r="J35" s="3">
         <v>-46300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -1664,17 +1421,8 @@
       <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1685,11 +1433,8 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,11 +1445,8 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1729,17 +1471,8 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1764,17 +1497,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1799,17 +1523,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1834,17 +1549,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1869,17 +1575,8 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1904,17 +1601,8 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1939,17 +1627,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1974,17 +1653,8 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2009,17 +1679,8 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2044,17 +1705,8 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3">
-        <v>0</v>
-      </c>
-      <c r="M50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2079,17 +1731,8 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2114,17 +1757,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2149,17 +1783,8 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3">
-        <v>0</v>
-      </c>
-      <c r="M53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2184,17 +1809,8 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2205,11 +1821,8 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2220,11 +1833,8 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2249,17 +1859,8 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2284,17 +1885,8 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2319,17 +1911,8 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2354,17 +1937,8 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2389,17 +1963,8 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2424,17 +1989,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2459,17 +2015,8 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3">
-        <v>0</v>
-      </c>
-      <c r="L63" s="3">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2494,17 +2041,8 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3">
-        <v>0</v>
-      </c>
-      <c r="L64" s="3">
-        <v>0</v>
-      </c>
-      <c r="M64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2529,17 +2067,8 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2564,17 +2093,8 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2585,11 +2105,8 @@
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2614,17 +2131,8 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3">
-        <v>0</v>
-      </c>
-      <c r="M68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2649,17 +2157,8 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3">
-        <v>0</v>
-      </c>
-      <c r="L69" s="3">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2684,17 +2183,8 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2719,17 +2209,8 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3">
-        <v>0</v>
-      </c>
-      <c r="M71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2754,17 +2235,8 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2789,17 +2261,8 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3">
-        <v>0</v>
-      </c>
-      <c r="L73" s="3">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2824,17 +2287,8 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3">
-        <v>0</v>
-      </c>
-      <c r="L74" s="3">
-        <v>0</v>
-      </c>
-      <c r="M74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2859,17 +2313,8 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3">
-        <v>0</v>
-      </c>
-      <c r="L75" s="3">
-        <v>0</v>
-      </c>
-      <c r="M75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -2894,17 +2339,8 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2929,22 +2365,13 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3">
-        <v>0</v>
-      </c>
-      <c r="L77" s="3">
-        <v>0</v>
-      </c>
-      <c r="M77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -2969,17 +2396,8 @@
       <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3004,17 +2422,8 @@
       <c r="J81" s="3">
         <v>-46300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3025,11 +2434,8 @@
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3"/>
-      <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3054,17 +2460,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3089,17 +2486,8 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3">
-        <v>0</v>
-      </c>
-      <c r="L84" s="3">
-        <v>0</v>
-      </c>
-      <c r="M84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3124,17 +2512,8 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3">
-        <v>0</v>
-      </c>
-      <c r="M85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3159,17 +2538,8 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3">
-        <v>0</v>
-      </c>
-      <c r="L86" s="3">
-        <v>0</v>
-      </c>
-      <c r="M86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3194,17 +2564,8 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3">
-        <v>0</v>
-      </c>
-      <c r="L87" s="3">
-        <v>0</v>
-      </c>
-      <c r="M87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3229,17 +2590,8 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3">
-        <v>0</v>
-      </c>
-      <c r="L88" s="3">
-        <v>0</v>
-      </c>
-      <c r="M88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3264,17 +2616,8 @@
       <c r="J89" s="3">
         <v>-14500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3285,11 +2628,8 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3314,17 +2654,8 @@
       <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3349,17 +2680,8 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3">
-        <v>0</v>
-      </c>
-      <c r="L92" s="3">
-        <v>0</v>
-      </c>
-      <c r="M92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3384,17 +2706,8 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3">
-        <v>0</v>
-      </c>
-      <c r="M93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3419,17 +2732,8 @@
       <c r="J94" s="3">
         <v>13000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3440,11 +2744,8 @@
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3469,17 +2770,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3504,17 +2796,8 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3">
-        <v>0</v>
-      </c>
-      <c r="L97" s="3">
-        <v>0</v>
-      </c>
-      <c r="M97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3539,17 +2822,8 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3">
-        <v>0</v>
-      </c>
-      <c r="L98" s="3">
-        <v>0</v>
-      </c>
-      <c r="M98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3574,17 +2848,8 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3">
-        <v>0</v>
-      </c>
-      <c r="L99" s="3">
-        <v>0</v>
-      </c>
-      <c r="M99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3609,17 +2874,8 @@
       <c r="J100" s="3">
         <v>25700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3644,17 +2900,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3678,15 +2925,6 @@
       </c>
       <c r="J102" s="3">
         <v>24000</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NAVN_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0196AF-066F-4925-86EE-E180A2E2DEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="NAVN" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>NAVN</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,138 +654,163 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:J102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>232800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>220200</v>
+      </c>
+      <c r="F8" s="3">
         <v>177900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>194900</v>
       </c>
-      <c r="F8" s="3">
-        <v>164700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>164700</v>
-      </c>
       <c r="H8" s="3">
+        <v>172000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>157500</v>
+      </c>
+      <c r="J8" s="3">
         <v>132000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>151100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>126900</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F9" s="3">
         <v>52100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>57100</v>
       </c>
-      <c r="F9" s="3">
-        <v>46300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>46300</v>
-      </c>
       <c r="H9" s="3">
+        <v>46900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>45700</v>
+      </c>
+      <c r="J9" s="3">
         <v>42700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>44500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>41300</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>172600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>163300</v>
+      </c>
+      <c r="F10" s="3">
         <v>125800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>137900</v>
       </c>
-      <c r="F10" s="3">
-        <v>118400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>118400</v>
-      </c>
       <c r="H10" s="3">
+        <v>125000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>111800</v>
+      </c>
+      <c r="J10" s="3">
         <v>89200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>106600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,34 +821,42 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F12" s="3">
         <v>35300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>51200</v>
       </c>
-      <c r="F12" s="3">
-        <v>32400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>32400</v>
-      </c>
       <c r="H12" s="3">
+        <v>33400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>31400</v>
+      </c>
+      <c r="J12" s="3">
         <v>31600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>33000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,60 +881,78 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F14" s="3">
         <v>8200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>97500</v>
       </c>
-      <c r="F14" s="3">
-        <v>10300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>10300</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>20500</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F15" s="3">
         <v>38400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
       </c>
-      <c r="F15" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2400</v>
-      </c>
       <c r="H15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -910,60 +960,74 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>235400</v>
+      </c>
+      <c r="F17" s="3">
         <v>259300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>274200</v>
       </c>
-      <c r="F17" s="3">
-        <v>178800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>178800</v>
-      </c>
       <c r="H17" s="3">
+        <v>184200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>173400</v>
+      </c>
+      <c r="J17" s="3">
         <v>164800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>170600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>154500</v>
       </c>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-81300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-79200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-14100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-14100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-32800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-19500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -974,138 +1038,170 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>30700</v>
       </c>
-      <c r="F20" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>5200</v>
-      </c>
       <c r="H20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-37800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-107800</v>
       </c>
-      <c r="F21" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-16900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-26800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-16700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-23800</v>
       </c>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F22" s="3">
         <v>3800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>15500</v>
       </c>
-      <c r="F22" s="3">
-        <v>16000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>16000</v>
-      </c>
       <c r="H22" s="3">
+        <v>15600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>16300</v>
+      </c>
+      <c r="J22" s="3">
         <v>18500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>19700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>18900</v>
       </c>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-82200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-221900</v>
       </c>
-      <c r="F23" s="3">
-        <v>-45900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-45900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-46500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-36700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-44100</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-9400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="F24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>4000</v>
-      </c>
       <c r="H24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1130,60 +1226,78 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-72800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-225400</v>
       </c>
-      <c r="F26" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-49900</v>
-      </c>
       <c r="H26" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-46700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-41900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-46300</v>
       </c>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-72800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-225400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-49900</v>
-      </c>
       <c r="H27" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-46700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-41900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-46300</v>
       </c>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1208,8 +1322,14 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1234,8 +1354,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1260,8 +1386,14 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1286,60 +1418,78 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F32" s="3">
         <v>5100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-30700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J32" s="3">
         <v>3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-72800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-225400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-49900</v>
-      </c>
       <c r="H33" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-46700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-41900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-46300</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1364,65 +1514,83 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-72800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-225400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-49900</v>
-      </c>
       <c r="H35" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-46700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-41900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-46300</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1433,8 +1601,10 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1445,46 +1615,54 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>653000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>518400</v>
+      </c>
+      <c r="F41" s="3">
         <v>583500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>809100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>223200</v>
       </c>
-      <c r="G41" s="3">
-        <v>223200</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>157700</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>162200</v>
+      </c>
+      <c r="F42" s="3">
         <v>157000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1497,8 +1675,14 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1506,25 +1690,31 @@
         <v>426400</v>
       </c>
       <c r="E43" s="3">
+        <v>448700</v>
+      </c>
+      <c r="F43" s="3">
+        <v>426400</v>
+      </c>
+      <c r="G43" s="3">
         <v>423400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>352200</v>
       </c>
-      <c r="G43" s="3">
-        <v>352200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>345800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1549,60 +1739,78 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F45" s="3">
         <v>39600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>43800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>36200</v>
       </c>
-      <c r="G45" s="3">
-        <v>36200</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>20300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1404600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1314800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1307000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1378400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>718900</v>
       </c>
-      <c r="G46" s="3">
-        <v>718900</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>688900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1627,60 +1835,78 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>78100</v>
+      </c>
+      <c r="F48" s="3">
         <v>78500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>74400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>74500</v>
       </c>
-      <c r="G48" s="3">
-        <v>74500</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>77500</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>254500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>255900</v>
+      </c>
+      <c r="F49" s="3">
         <v>260600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>287500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>291000</v>
       </c>
-      <c r="G49" s="3">
-        <v>291000</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>275400</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1705,8 +1931,14 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1731,34 +1963,46 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>33400</v>
+      </c>
+      <c r="F52" s="3">
         <v>33600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>29700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>29000</v>
       </c>
-      <c r="G52" s="3">
-        <v>29000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>26000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1783,34 +2027,46 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1811100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1714200</v>
+      </c>
+      <c r="F54" s="3">
         <v>1708800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1792700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1134400</v>
       </c>
-      <c r="G54" s="3">
-        <v>1134400</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>1084000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1821,8 +2077,10 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1833,164 +2091,202 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-    </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>62900</v>
+      </c>
+      <c r="F57" s="3">
         <v>65900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>62300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>48200</v>
       </c>
-      <c r="G57" s="3">
-        <v>48200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>42800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F58" s="3">
         <v>12600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>11500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>12700</v>
       </c>
-      <c r="G58" s="3">
-        <v>12700</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>232300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>142100</v>
+      </c>
+      <c r="F59" s="3">
         <v>156100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>126600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>114900</v>
       </c>
-      <c r="G59" s="3">
-        <v>114900</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>108400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>305000</v>
+      </c>
+      <c r="F60" s="3">
         <v>320900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>307100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>249200</v>
       </c>
-      <c r="G60" s="3">
-        <v>249200</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>446000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>155900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>158700</v>
+      </c>
+      <c r="F61" s="3">
         <v>161800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>242800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>697900</v>
       </c>
-      <c r="G61" s="3">
-        <v>697900</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>440100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F62" s="3">
         <v>17000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>15900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>85300</v>
       </c>
-      <c r="G62" s="3">
-        <v>85300</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>75100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2015,8 +2311,14 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2041,8 +2343,14 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2067,34 +2375,46 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>495400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>477600</v>
+      </c>
+      <c r="F66" s="3">
         <v>500700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>573800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1041700</v>
       </c>
-      <c r="G66" s="3">
-        <v>1041700</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>969700</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2105,8 +2425,10 @@
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2131,8 +2453,14 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2157,8 +2485,14 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2169,22 +2503,28 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>1301100</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>1301100</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>1301100</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>1301100</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.2">
+        <v>1301100</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2209,34 +2549,46 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2064800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-2035600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-2015100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1942400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1717000</v>
       </c>
-      <c r="G72" s="3">
-        <v>-1717000</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-1617100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2261,8 +2613,14 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2287,8 +2645,14 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2313,34 +2677,46 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1315700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1236600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1208100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1218800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1208500</v>
       </c>
-      <c r="G76" s="3">
-        <v>-1208500</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1186900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="J76" s="3">
+        <v>-1186900</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2365,65 +2741,83 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
     </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-72800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-225400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-49900</v>
-      </c>
       <c r="H81" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-46700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-41900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-46300</v>
       </c>
     </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2434,34 +2828,42 @@
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
-    </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="3">
         <v>1300</v>
       </c>
       <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>1300</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2486,8 +2888,14 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2512,8 +2920,14 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2538,8 +2952,14 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2564,8 +2984,14 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2590,34 +3016,46 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="F89" s="3">
         <v>35000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6100</v>
       </c>
-      <c r="F89" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G89" s="3">
-        <v>2400</v>
-      </c>
       <c r="H89" s="3">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-8900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-12400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-14500</v>
       </c>
     </row>
-    <row r="90" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2628,34 +3066,42 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
-    </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2680,8 +3126,14 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2706,34 +3158,46 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-153500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-38500</v>
       </c>
-      <c r="F94" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H94" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J94" s="3">
         <v>42000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-23200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2744,8 +3208,10 @@
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
-    </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2770,8 +3236,14 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2796,8 +3268,14 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2822,8 +3300,14 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2848,82 +3332,106 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-110700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>624000</v>
       </c>
-      <c r="F100" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>3300</v>
-      </c>
       <c r="H100" s="3">
+        <v>-55400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>62000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-25100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>26300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="101" spans="3:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-227200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>579700</v>
       </c>
-      <c r="F102" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>2500</v>
-      </c>
       <c r="H102" s="3">
+        <v>-63600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>68500</v>
+      </c>
+      <c r="J102" s="3">
         <v>4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>24000</v>
       </c>
     </row>
